--- a/grupos/3APV - Estadisticos 20241.xlsx
+++ b/grupos/3APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -164,18 +164,18 @@
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
@@ -191,33 +191,42 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>IBARRA</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BALCAZAR</t>
+  </si>
+  <si>
+    <t>BERTELY</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUCIANO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>PALOMARES</t>
   </si>
   <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BALCAZAR</t>
-  </si>
-  <si>
-    <t>BERTELY</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUCIANO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -227,10 +236,16 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ZAYAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>APALE</t>
   </si>
   <si>
     <t>OLIVARES</t>
@@ -251,31 +266,40 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>DANIEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUIS PABLO</t>
+  </si>
+  <si>
     <t>ARMANDO</t>
   </si>
   <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JURISEL</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
+    <t>KEVIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>MICHEL LEONEL</t>
+  </si>
+  <si>
     <t>JUSTIN GIOVANNI</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ABRAHAN</t>
-  </si>
-  <si>
-    <t>KEVIN SANTIAGO</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -830,28 +854,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -881,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -893,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="AE4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF4">
         <v>7</v>
@@ -931,28 +955,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1032,28 +1056,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1080,16 +1104,16 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD6">
         <v>7</v>
@@ -1098,7 +1122,7 @@
         <v>9</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG6">
         <v>-1</v>
@@ -1133,28 +1157,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1187,7 +1211,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1196,7 +1220,7 @@
         <v>9</v>
       </c>
       <c r="AE7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF7">
         <v>8</v>
@@ -1234,28 +1258,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1288,19 +1312,19 @@
         <v>9</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD8">
         <v>5</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8">
         <v>-1</v>
@@ -1335,28 +1359,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1386,10 +1410,10 @@
         <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -1436,28 +1460,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1484,7 +1508,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1499,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF10">
         <v>8</v>
@@ -1537,28 +1561,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1588,10 +1612,10 @@
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1600,7 +1624,7 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF11">
         <v>10</v>
@@ -1638,28 +1662,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1686,13 +1710,13 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>8</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>9</v>
@@ -1701,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="AE12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF12">
         <v>9</v>
@@ -1739,28 +1763,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1787,13 +1811,13 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>9</v>
@@ -1805,7 +1829,7 @@
         <v>8</v>
       </c>
       <c r="AF13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>-1</v>
@@ -1840,28 +1864,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1891,19 +1915,19 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>6</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>8</v>
@@ -1941,28 +1965,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1995,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>8</v>
@@ -2007,7 +2031,7 @@
         <v>9</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG15">
         <v>-1</v>
@@ -2042,28 +2066,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2108,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG16">
         <v>-1</v>
@@ -2143,28 +2167,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2191,25 +2215,25 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD17">
         <v>6</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG17">
         <v>-1</v>
@@ -2244,28 +2268,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2310,7 +2334,7 @@
         <v>5</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2345,28 +2369,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2396,7 +2420,7 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2408,10 +2432,10 @@
         <v>7</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG19">
         <v>-1</v>
@@ -2446,28 +2470,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2509,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="AE20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF20">
         <v>9</v>
@@ -2547,28 +2571,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2598,7 +2622,7 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>9</v>
@@ -2610,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="AE21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF21">
         <v>10</v>
@@ -2648,28 +2672,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2699,10 +2723,10 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2711,10 +2735,10 @@
         <v>6</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG22">
         <v>-1</v>
@@ -2898,10 +2922,10 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -2922,10 +2946,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X4">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -2960,49 +2984,49 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>75</v>
+        <v>38.8</v>
       </c>
       <c r="K5">
-        <v>84.40000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="M5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="P5">
-        <v>91.7</v>
+        <v>47.8</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>75</v>
+        <v>38.8</v>
       </c>
       <c r="S5">
-        <v>84.40000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="U5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="X5">
-        <v>91.7</v>
+        <v>47.8</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -3040,19 +3064,19 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N6">
         <v>87.5</v>
       </c>
       <c r="O6">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3064,19 +3088,19 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="V6">
         <v>87.5</v>
       </c>
       <c r="W6">
-        <v>66.7</v>
+        <v>78.8</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -3194,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3206,10 +3230,10 @@
         <v>93.8</v>
       </c>
       <c r="O8">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="P8">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3218,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -3230,10 +3254,10 @@
         <v>93.8</v>
       </c>
       <c r="W8">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="X8">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -3268,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3277,7 +3301,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -3286,13 +3310,13 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3301,7 +3325,7 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3310,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="X9">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y9">
         <v>100</v>
@@ -3348,22 +3372,22 @@
         <v>95</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L10">
         <v>100</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="N10">
         <v>93.8</v>
       </c>
       <c r="O10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P10">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3372,22 +3396,22 @@
         <v>95</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="T10">
         <v>100</v>
       </c>
       <c r="U10">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="V10">
         <v>93.8</v>
       </c>
       <c r="W10">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X10">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -3422,49 +3446,49 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="K11">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P11">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.5</v>
+        <v>98.8</v>
       </c>
       <c r="S11">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="T11">
         <v>100</v>
       </c>
       <c r="U11">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X11">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -3502,23 +3526,23 @@
         <v>100</v>
       </c>
       <c r="K12">
+        <v>96.7</v>
+      </c>
+      <c r="L12">
+        <v>100</v>
+      </c>
+      <c r="M12">
+        <v>100</v>
+      </c>
+      <c r="N12">
+        <v>100</v>
+      </c>
+      <c r="O12">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="P12">
         <v>97.8</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12">
-        <v>83.3</v>
-      </c>
-      <c r="P12">
-        <v>95.8</v>
-      </c>
       <c r="Q12">
         <v>100</v>
       </c>
@@ -3526,22 +3550,22 @@
         <v>100</v>
       </c>
       <c r="S12">
+        <v>96.7</v>
+      </c>
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="X12">
         <v>97.8</v>
-      </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
-      <c r="U12">
-        <v>100</v>
-      </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-      <c r="W12">
-        <v>83.3</v>
-      </c>
-      <c r="X12">
-        <v>95.8</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -3579,19 +3603,19 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>83.3</v>
+        <v>78.8</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -3603,19 +3627,19 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>83.3</v>
+        <v>78.8</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -3662,16 +3686,16 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N14">
         <v>81.3</v>
       </c>
       <c r="O14">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="P14">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3686,16 +3710,16 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V14">
         <v>81.3</v>
       </c>
       <c r="W14">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="X14">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -3733,19 +3757,19 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N15">
         <v>93.8</v>
       </c>
       <c r="O15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -3757,19 +3781,19 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T15">
         <v>100</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V15">
         <v>93.8</v>
       </c>
       <c r="W15">
-        <v>94.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -3810,22 +3834,22 @@
         <v>97.5</v>
       </c>
       <c r="K16">
-        <v>95.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N16">
         <v>93.8</v>
       </c>
       <c r="O16">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3834,22 +3858,22 @@
         <v>97.5</v>
       </c>
       <c r="S16">
-        <v>95.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
       </c>
       <c r="U16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="V16">
         <v>93.8</v>
       </c>
       <c r="W16">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="X16">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -3887,7 +3911,7 @@
         <v>95</v>
       </c>
       <c r="K17">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3899,10 +3923,10 @@
         <v>93.8</v>
       </c>
       <c r="O17">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3911,7 +3935,7 @@
         <v>95</v>
       </c>
       <c r="S17">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -3923,10 +3947,10 @@
         <v>93.8</v>
       </c>
       <c r="W17">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X17">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -3964,7 +3988,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -3976,7 +4000,7 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -3988,7 +4012,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -4000,7 +4024,7 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X18">
         <v>100</v>
@@ -4041,7 +4065,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4053,7 +4077,7 @@
         <v>93.8</v>
       </c>
       <c r="O19">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4065,7 +4089,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T19">
         <v>100</v>
@@ -4077,7 +4101,7 @@
         <v>93.8</v>
       </c>
       <c r="W19">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -4130,7 +4154,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4154,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>88.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -4195,7 +4219,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4207,7 +4231,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4219,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -4231,7 +4255,7 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X21">
         <v>100</v>
@@ -4284,10 +4308,10 @@
         <v>93.8</v>
       </c>
       <c r="O22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P22">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4308,10 +4332,10 @@
         <v>93.8</v>
       </c>
       <c r="W22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X22">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -4441,19 +4465,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>68.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G4" s="2">
-        <v>31.6</v>
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4464,7 +4488,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4473,19 +4497,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>73.7</v>
+        <v>89.5</v>
       </c>
       <c r="G5" s="2">
-        <v>26.3</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4496,7 +4520,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4517,7 +4541,7 @@
         <v>10.5</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4528,7 +4552,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4549,7 +4573,7 @@
         <v>10.5</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4560,7 +4584,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -4613,7 +4637,7 @@
         <v>5.3</v>
       </c>
       <c r="H9">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4663,7 +4687,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4695,16 +4719,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920295</v>
+        <v>23330051920285</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4718,16 +4742,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920295</v>
+        <v>23330051920285</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -4741,22 +4765,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920308</v>
+        <v>23330051920294</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4764,16 +4788,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920308</v>
+        <v>23330051920294</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -4787,39 +4811,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920281</v>
+        <v>23330051920295</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920283</v>
+        <v>23330051920295</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -4833,39 +4857,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920284</v>
+        <v>23330051920320</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920292</v>
+        <v>23330051920320</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -4879,16 +4903,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920365</v>
+        <v>23330051920281</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -4902,16 +4926,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920296</v>
+        <v>23330051920283</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -4925,16 +4949,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920299</v>
+        <v>23330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>12</v>
@@ -4948,16 +4972,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920348</v>
+        <v>23330051920292</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -4971,16 +4995,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920363</v>
+        <v>23330051920365</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>12</v>
@@ -4994,16 +5018,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920326</v>
+        <v>23330051920296</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -5012,6 +5036,121 @@
         <v>45</v>
       </c>
       <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920299</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920308</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920348</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920363</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920326</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20241.xlsx
+++ b/grupos/3APV - Estadisticos 20241.xlsx
@@ -866,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -914,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE4">
         <v>9</v>
@@ -967,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1068,7 +1068,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>9</v>
@@ -1116,7 +1116,7 @@
         <v>8</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE6">
         <v>9</v>
@@ -1169,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>9</v>
@@ -1371,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>9</v>
@@ -1674,7 +1674,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1823,7 +1823,7 @@
         <v>9</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>8</v>
@@ -1876,7 +1876,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>9</v>
@@ -1924,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>8</v>
@@ -1977,7 +1977,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>9</v>
@@ -2078,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2179,7 +2179,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2227,7 +2227,7 @@
         <v>9</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE17">
         <v>8</v>
@@ -2280,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -2381,7 +2381,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>9</v>
@@ -2429,7 +2429,7 @@
         <v>8</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE19">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="AD20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>9</v>
@@ -2583,7 +2583,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>9</v>
@@ -2684,7 +2684,7 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2732,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE22">
         <v>8</v>
@@ -2996,7 +2996,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O5">
         <v>72.7</v>
@@ -3020,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="W5">
         <v>72.7</v>
@@ -3458,7 +3458,7 @@
         <v>92.5</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11">
         <v>81.8</v>
@@ -3482,7 +3482,7 @@
         <v>92.5</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W11">
         <v>81.8</v>
@@ -3689,7 +3689,7 @@
         <v>97.5</v>
       </c>
       <c r="N14">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O14">
         <v>84.8</v>
@@ -3713,7 +3713,7 @@
         <v>97.5</v>
       </c>
       <c r="V14">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="W14">
         <v>84.8</v>
@@ -3766,7 +3766,7 @@
         <v>97.5</v>
       </c>
       <c r="N15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O15">
         <v>97</v>
@@ -3790,7 +3790,7 @@
         <v>97.5</v>
       </c>
       <c r="V15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W15">
         <v>97</v>
@@ -3843,7 +3843,7 @@
         <v>97.5</v>
       </c>
       <c r="N16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O16">
         <v>72.7</v>
@@ -3867,7 +3867,7 @@
         <v>97.5</v>
       </c>
       <c r="V16">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W16">
         <v>72.7</v>
@@ -3920,7 +3920,7 @@
         <v>95</v>
       </c>
       <c r="N17">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O17">
         <v>93.90000000000001</v>
@@ -3944,7 +3944,7 @@
         <v>95</v>
       </c>
       <c r="V17">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W17">
         <v>93.90000000000001</v>
@@ -3997,7 +3997,7 @@
         <v>90</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O18">
         <v>81.8</v>
@@ -4021,7 +4021,7 @@
         <v>90</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W18">
         <v>81.8</v>
@@ -4074,7 +4074,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O19">
         <v>93.90000000000001</v>
@@ -4098,7 +4098,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W19">
         <v>93.90000000000001</v>
@@ -4305,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O22">
         <v>90.90000000000001</v>
@@ -4329,7 +4329,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W22">
         <v>90.90000000000001</v>
@@ -4445,7 +4445,7 @@
         <v>36.8</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/3APV - Estadisticos 20241.xlsx
+++ b/grupos/3APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -191,6 +191,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>ESTRADA</t>
   </si>
   <si>
@@ -225,6 +228,9 @@
   </si>
   <si>
     <t>APALE</t>
+  </si>
+  <si>
+    <t>CARLOS</t>
   </si>
   <si>
     <t>JOSE MARCOS</t>
@@ -4185,7 +4191,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4217,22 +4223,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920317</v>
+        <v>23330051920301</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4240,16 +4246,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920317</v>
+        <v>23330051920301</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4263,22 +4269,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920309</v>
+        <v>23330051920301</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4286,22 +4292,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920309</v>
+        <v>23330051920301</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4309,22 +4315,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920285</v>
+        <v>23330051920317</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
         <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4332,16 +4338,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920294</v>
+        <v>23330051920317</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4355,16 +4361,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920295</v>
+        <v>23330051920309</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -4378,24 +4384,116 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>23330051920309</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920285</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920294</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920295</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
         <v>23330051920320</v>
       </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
         <v>48</v>
       </c>
-      <c r="G9">
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20241.xlsx
+++ b/grupos/3APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -155,16 +155,19 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
+    <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
@@ -173,9 +176,6 @@
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -194,58 +194,25 @@
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>PELAYO</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>IBARRA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZAYAS</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
     <t>CARLOS</t>
   </si>
   <si>
-    <t>JOSE MARCOS</t>
-  </si>
-  <si>
     <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS PABLO</t>
-  </si>
-  <si>
-    <t>ARMANDO</t>
   </si>
   <si>
     <t>VALERIA</t>
@@ -796,31 +763,31 @@
         <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -835,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -885,25 +852,25 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -974,25 +941,25 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1007,13 +974,13 @@
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1063,31 +1030,31 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1152,46 +1119,46 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8">
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1241,46 +1208,46 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1330,25 +1297,25 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1357,13 +1324,13 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <v>9</v>
       </c>
       <c r="AA10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>8</v>
@@ -1419,40 +1386,40 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>9</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>7</v>
@@ -1508,46 +1475,46 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1597,31 +1564,31 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1636,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1686,34 +1653,34 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
         <v>10</v>
@@ -1725,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1775,25 +1742,25 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1802,13 +1769,13 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -1864,46 +1831,46 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1953,28 +1920,28 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2042,40 +2009,40 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2131,25 +2098,25 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2164,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2220,31 +2187,31 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2259,7 +2226,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2309,28 +2276,28 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2342,13 +2309,13 @@
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2398,31 +2365,31 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2437,7 +2404,7 @@
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2612,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -2627,7 +2594,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V4">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2677,25 +2644,25 @@
         <v>47.8</v>
       </c>
       <c r="P5">
-        <v>38.8</v>
+        <v>25</v>
       </c>
       <c r="Q5">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="R5">
-        <v>87.8</v>
+        <v>91.8</v>
       </c>
       <c r="S5">
         <v>10</v>
       </c>
       <c r="T5">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U5">
         <v>72.7</v>
       </c>
       <c r="V5">
-        <v>47.8</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2748,7 +2715,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>97.8</v>
+        <v>97.2</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -2757,7 +2724,7 @@
         <v>90</v>
       </c>
       <c r="T6">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U6">
         <v>78.8</v>
@@ -2884,7 +2851,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -2893,13 +2860,13 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="U8">
         <v>87.90000000000001</v>
       </c>
       <c r="V8">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -2949,7 +2916,7 @@
         <v>97.8</v>
       </c>
       <c r="P9">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -2967,7 +2934,7 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3017,10 +2984,10 @@
         <v>97.8</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="Q10">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3029,13 +2996,13 @@
         <v>92.5</v>
       </c>
       <c r="T10">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="U10">
         <v>90.90000000000001</v>
       </c>
       <c r="V10">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3079,16 +3046,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="N11">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O11">
         <v>97.8</v>
       </c>
       <c r="P11">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="Q11">
-        <v>97.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3097,13 +3064,13 @@
         <v>92.5</v>
       </c>
       <c r="T11">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U11">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V11">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3156,7 +3123,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -3171,7 +3138,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="V12">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3224,7 +3191,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>97.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3301,13 +3268,13 @@
         <v>97.5</v>
       </c>
       <c r="T14">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="U14">
         <v>84.8</v>
       </c>
       <c r="V14">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3360,7 +3327,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>98.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3369,7 +3336,7 @@
         <v>97.5</v>
       </c>
       <c r="T15">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U15">
         <v>97</v>
@@ -3398,7 +3365,7 @@
         <v>93.8</v>
       </c>
       <c r="G16">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>100</v>
@@ -3419,16 +3386,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="N16">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="O16">
         <v>97.8</v>
       </c>
       <c r="P16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q16">
-        <v>94.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3437,13 +3404,13 @@
         <v>97.5</v>
       </c>
       <c r="T16">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U16">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="V16">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3493,10 +3460,10 @@
         <v>97.8</v>
       </c>
       <c r="P17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>98.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -3505,13 +3472,13 @@
         <v>95</v>
       </c>
       <c r="T17">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U17">
         <v>93.90000000000001</v>
       </c>
       <c r="V17">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3534,7 +3501,7 @@
         <v>100</v>
       </c>
       <c r="G18">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -3555,7 +3522,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="N18">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3564,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -3573,10 +3540,10 @@
         <v>90</v>
       </c>
       <c r="T18">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U18">
-        <v>81.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3632,7 +3599,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>98.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -3641,7 +3608,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U19">
         <v>93.90000000000001</v>
@@ -3768,7 +3735,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3845,13 +3812,13 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U22">
         <v>90.90000000000001</v>
       </c>
       <c r="V22">
-        <v>97.8</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3908,7 +3875,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -3917,19 +3884,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>63.2</v>
+        <v>84.2</v>
       </c>
       <c r="G2" s="2">
-        <v>36.8</v>
+        <v>15.8</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3940,7 +3907,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -3949,19 +3916,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>84.2</v>
+        <v>89.5</v>
       </c>
       <c r="G3" s="2">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3981,19 +3948,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G4" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4004,7 +3971,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
@@ -4013,19 +3980,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G5" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4036,7 +4003,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -4045,19 +4012,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G6" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4068,7 +4035,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -4077,16 +4044,16 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G7" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H7">
         <v>7.5</v>
@@ -4100,7 +4067,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
@@ -4121,7 +4088,7 @@
         <v>5.3</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4191,7 +4158,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4232,13 +4199,13 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4246,19 +4213,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920301</v>
+        <v>23330051920309</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>45</v>
@@ -4269,231 +4236,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920301</v>
+        <v>23330051920320</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>46</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920301</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920317</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920317</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920309</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920309</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920285</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920294</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920295</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920320</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20241.xlsx
+++ b/grupos/3APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="57">
   <si>
     <t>Materia</t>
   </si>
@@ -155,15 +155,15 @@
     <t>Recursos socioemocionales III</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
@@ -189,33 +189,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PELAYO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>IVAN JESUS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -772,13 +745,13 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -861,13 +834,13 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -950,13 +923,13 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1039,13 +1012,13 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1128,13 +1101,13 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1217,13 +1190,13 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1306,13 +1279,13 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1327,13 +1300,13 @@
         <v>6</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1395,13 +1368,13 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1422,7 +1395,7 @@
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1484,13 +1457,13 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1505,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1573,13 +1546,13 @@
         <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1594,7 +1567,7 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1662,13 +1635,13 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1683,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1751,13 +1724,13 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1772,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -1840,13 +1813,13 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1867,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1929,13 +1902,13 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1950,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>7</v>
@@ -2018,13 +1991,13 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2045,7 +2018,7 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2107,13 +2080,13 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2128,7 +2101,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2196,13 +2169,13 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2285,13 +2258,13 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2312,7 +2285,7 @@
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2374,13 +2347,13 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2395,7 +2368,7 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2585,13 +2558,13 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V4">
         <v>98.40000000000001</v>
@@ -2653,13 +2626,13 @@
         <v>91.8</v>
       </c>
       <c r="S5">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="T5">
         <v>87.5</v>
       </c>
       <c r="U5">
-        <v>72.7</v>
+        <v>81.3</v>
       </c>
       <c r="V5">
         <v>59.4</v>
@@ -2721,13 +2694,13 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T6">
         <v>91.7</v>
       </c>
       <c r="U6">
-        <v>78.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -2789,7 +2762,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -2857,13 +2830,13 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T8">
         <v>95.8</v>
       </c>
       <c r="U8">
-        <v>87.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="V8">
         <v>98.40000000000001</v>
@@ -2925,7 +2898,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -2993,13 +2966,13 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="T10">
         <v>95.8</v>
       </c>
       <c r="U10">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V10">
         <v>98.40000000000001</v>
@@ -3061,13 +3034,13 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="T11">
         <v>97.90000000000001</v>
       </c>
       <c r="U11">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
         <v>98.40000000000001</v>
@@ -3129,13 +3102,13 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="T12">
         <v>100</v>
       </c>
       <c r="U12">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V12">
         <v>98.40000000000001</v>
@@ -3197,13 +3170,13 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T13">
         <v>100</v>
       </c>
       <c r="U13">
-        <v>78.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -3265,13 +3238,13 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="T14">
         <v>93.8</v>
       </c>
       <c r="U14">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="V14">
         <v>98.40000000000001</v>
@@ -3333,13 +3306,13 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T15">
         <v>97.90000000000001</v>
       </c>
       <c r="U15">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -3401,7 +3374,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="T16">
         <v>97.90000000000001</v>
@@ -3469,13 +3442,13 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="T17">
         <v>97.90000000000001</v>
       </c>
       <c r="U17">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V17">
         <v>98.40000000000001</v>
@@ -3537,13 +3510,13 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="T18">
         <v>97.90000000000001</v>
       </c>
       <c r="U18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3605,13 +3578,13 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T19">
         <v>97.90000000000001</v>
       </c>
       <c r="U19">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -3679,7 +3652,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>93.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -3747,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -3815,7 +3788,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="U22">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="V22">
         <v>98.40000000000001</v>
@@ -3875,7 +3848,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>45</v>
@@ -3884,19 +3857,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>84.2</v>
+        <v>94.7</v>
       </c>
       <c r="G2" s="2">
-        <v>15.8</v>
+        <v>5.3</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3916,19 +3889,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>89.5</v>
+        <v>94.7</v>
       </c>
       <c r="G3" s="2">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3939,7 +3912,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -3960,7 +3933,7 @@
         <v>5.3</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4158,7 +4131,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4188,75 +4161,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920301</v>
-      </c>
-      <c r="B2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920309</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920320</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
